--- a/erp-server/erp-server-tms/src/main/resources/excel/firstMileWeightChangeExportError.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/firstMileWeightChangeExportError.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>来源单号</t>
   </si>
@@ -115,6 +115,36 @@
   </si>
   <si>
     <t>错误信息</t>
+  </si>
+  <si>
+    <t>{.sourceCode}</t>
+  </si>
+  <si>
+    <t>{.transportNo}</t>
+  </si>
+  <si>
+    <t>{.businessCode}</t>
+  </si>
+  <si>
+    <t>{.boxNoStr}</t>
+  </si>
+  <si>
+    <t>{.platformSkuNo}</t>
+  </si>
+  <si>
+    <t>{.skuNo}</t>
+  </si>
+  <si>
+    <t>{.productWeightStr}</t>
+  </si>
+  <si>
+    <t>{.outStockWeightStr}</t>
+  </si>
+  <si>
+    <t>{.outStockSizeStr}</t>
+  </si>
+  <si>
+    <t>{.errorMsg}</t>
   </si>
 </sst>
 </file>
@@ -1089,8 +1119,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="15.875" customWidth="1"/>
     <col min="2" max="2" width="20.25" customWidth="1"/>
@@ -1134,6 +1164,38 @@
       </c>
       <c r="J1" s="1" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/firstMileWeightChangeExportError.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/firstMileWeightChangeExportError.xlsx
@@ -41,17 +41,11 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Courier New"/>
-        <charset val="134"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="11"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
@@ -60,17 +54,11 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Courier New"/>
-        <charset val="134"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="11"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
@@ -78,7 +66,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="11"/>
         <rFont val="Courier New"/>
         <charset val="134"/>
       </rPr>
@@ -87,17 +75,11 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Courier New"/>
-        <charset val="134"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="11"/>
         <rFont val="Courier New"/>
         <charset val="134"/>
       </rPr>
@@ -159,7 +141,7 @@
     <numFmt numFmtId="176" formatCode="0_ "/>
     <numFmt numFmtId="177" formatCode="0.000000_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -174,12 +156,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9.8"/>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Courier New"/>
       <charset val="134"/>
@@ -329,12 +311,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Courier New"/>
       <charset val="134"/>
     </font>
@@ -1134,7 +1111,7 @@
     <col min="10" max="10" width="26.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:10">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:10">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>

--- a/erp-server/erp-server-tms/src/main/resources/excel/firstMileWeightChangeExportError.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/firstMileWeightChangeExportError.xlsx
@@ -41,6 +41,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -54,6 +60,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -75,6 +87,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -102,10 +120,10 @@
     <t>{.sourceCode}</t>
   </si>
   <si>
+    <t>{.businessCode}</t>
+  </si>
+  <si>
     <t>{.transportNo}</t>
-  </si>
-  <si>
-    <t>{.businessCode}</t>
   </si>
   <si>
     <t>{.boxNoStr}</t>
